--- a/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
+++ b/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
@@ -620,7 +620,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Projektkoordination &amp; Vereinsführung (Obmann); Gesamtarchitektur der Plattform Strom für alle</t>
+          <t>Vereinsführung, Netzbetreiber-Vertrag &amp; Tarife (Obmann); Gesamtarchitektur &amp; Projektleitung; Sicherheit &amp; Datenschutz der Plattform Strom für alle</t>
         </is>
       </c>
     </row>
@@ -670,8 +670,8 @@
       <c r="D9" s="8" t="n"/>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Fabian Amlacher (Abteilung: Elektrotechnik) – Kassier; Infrastruktur, Frontend, ESP32-Firmware-Pipeline
-Alexander Brunner (Abteilung: Elektrotechnik) – Gründungsmitglied; EDA-Datenimport, Abrechnungslogik</t>
+          <t>Fabian Amlacher (Abteilung: Elektrotechnik) – Kassier; Web-Frontend &amp; -Backend, Serverinfrastruktur (Docker, Datenbank, Backup), EDA-Datenimport, Abrechnungslogik (Rechnungserstellung, SEPA-Lastschrift)
+Alexander Brunner (Abteilung: Elektrotechnik) – Gründungsmitglied; Hardware &amp; Firmware der selbst gebauten P1-Ausleseeinheit (Platine, 3D-Druck, P1-Schnittstelle, MQTT, WLAN)</t>
         </is>
       </c>
     </row>
@@ -776,9 +776,9 @@
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Gemeinsam: Aufbau der Plattform „Strom für alle“ – einer mandantenfähigen Webanwendung zur Verwaltung mehrerer Energiegemeinschaften (Mitglieder, Zählpunkte, Verträge, Tarife, Abrechnung) auf Basis von PostgreSQL/TimescaleDB, PHP, nginx/Traefik und Docker. Gemeinsam wird untersucht, wie Echtzeit-Messdaten (ESP32/P1-Schnittstelle) und die offiziellen EDA-Verrechnungsdaten des Netzbetreibers sauber getrennt und für Visualisierung bzw. rechtssichere Abrechnung genutzt werden können, sowie wie eine EAG-/ElWOG-konforme, dynamische Verteilung nach Viertelstundenwerten technisch und organisatorisch umgesetzt wird.
-Patrick Ropper (Obmann): Projektkoordination und Entscheidungsfindung im Team; Gründung und laufende Führung der Pilot-EEG (Statuten, Vertrag mit dem Netzbetreiber KNG-Kärnten Netz, Tarifgestaltung); Gesamtarchitektur der Plattform sowie Schnittstelle zwischen technischer Umsetzung, rechtlichen Vorgaben (VerG, ElWOG, EAG, UStG) und steuerlicher Beratung.
-Fabian Amlacher (Kassier): Aufbau der Serverinfrastruktur (Docker, Traefik, MQTT/Mosquitto); Entwicklung des Frontends der Plattform; Entwicklung und Test der ESP32-Firmware zum Auslesen der P1-Schnittstelle intelligenter Stromzähler sowie der MQTT-Datenpipeline von der Messstelle bis in die Datenbank.
-Alexander Brunner: Entwicklung der Importlogik für die manuellen EDA-XLSX-Exporte des Netzbetreibers (rechtliche Verrechnungsdatenbasis) sowie der Abrechnungslogik der Plattform (quartalsweise/jährliche Verrechnung von Bezug und Einspeisung je Mitglied).</t>
+Patrick Ropper (Obmann): Projektkoordination und Entscheidungsfindung im Team; Gründung und laufende Führung der Pilot-EEG (Statuten, Vertrag mit dem Netzbetreiber KNG-Kärnten Netz inkl. Festlegung des Aufteilungsschlüssels, Tarifgestaltung, steuerliche Beratung); Gesamtarchitektur der Plattform sowie Schnittstelle zwischen technischer Umsetzung und rechtlichen Vorgaben (VerG, ElWOG, EAG, UStG); Sicherheit &amp; Datenschutz (DSGVO, Verschlüsselung, Zugriffsschutz, Demo-Modus) in enger Abstimmung mit Fabian (Webseite) und Alexander (Ausleseeinheit); rechtlich vorgeschriebener Rechnungsinhalt und Rechnungsdesign.
+Fabian Amlacher (Kassier): Aufbau der Serverinfrastruktur (Docker, Traefik, MQTT/Mosquitto, PostgreSQL/TimescaleDB, Backup); Entwicklung von Frontend und Backend der Plattform (Mitgliederverwaltung, Live-Anzeige); Import der manuellen EDA-XLSX-Exporte des Netzbetreibers und Zuordnung der Verbrauchs-/Einspeisewerte je Zählpunkt in der Datenbank; Abrechnungslogik inkl. Rechnungserstellung über einen LaTeX-zu-PDF-Service und Erstellung der SEPA-Lastschrift-Datei für den Bankeinzug.
+Alexander Brunner: Entwicklung von Hardware (Platinen-Design, Bauteilauswahl, 3D-Druck-Gehäuse) und Firmware (P1-Schnittstelle intelligenter Stromzähler, MQTT-Übertragung, WLAN-Setup) der selbst gebauten P1-Ausleseeinheit sowie deren Inbetriebnahme und Test.</t>
         </is>
       </c>
     </row>
@@ -832,9 +832,9 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Patrick Ropper: Eine im Verein eingetragene und beim Netzbetreiber aktive Energiegemeinschaft (Statuten, Mitgliederverträge, Tarifblatt, AGB) sowie eine dokumentierte Gesamtarchitektur und Projektsteuerung der Plattform Strom für alle.
-Fabian Amlacher: Ein lauffähiges Frontend der Plattform sowie eine funktionierende ESP32-Firmware inklusive MQTT-Pipeline, die Echtzeit-Leistungsdaten mehrerer Zählpunkte zuverlässig in die Datenbank überträgt.
-Alexander Brunner: Ein funktionierender Import der EDA-Verrechnungsdaten sowie eine automatisierte Abrechnungslogik, die aus den importierten Viertelstundenwerten korrekte, EAG-konforme Rechnungen je Mitglied erzeugt.</t>
+          <t>Patrick Ropper: Eine im Verein eingetragene und beim Netzbetreiber aktive Energiegemeinschaft (Statuten, Mitgliederverträge, Tarifblatt, AGB), eine dokumentierte Gesamtarchitektur und Projektsteuerung sowie ein datenschutz- und sicherheitskonform umgesetztes Konzept (DSGVO, Verschlüsselung, Zugriffsschutz) der Plattform Strom für alle.
+Fabian Amlacher: Ein lauffähiges Frontend und Backend der Plattform samt Serverinfrastruktur (Docker, Datenbank, Backup) sowie ein funktionierender EDA-Datenimport und eine automatisierte Abrechnungslogik inkl. Rechnungserstellung (LaTeX zu PDF) und SEPA-Lastschrift-Export.
+Alexander Brunner: Eine selbst entwickelte und gefertigte P1-Ausleseeinheit (Platine, 3D-gedrucktes Gehäuse) mit funktionierender Firmware (P1-Schnittstelle, MQTT-Übertragung, WLAN-Konfiguration), einsatzbereit bei den Mitgliedern der Pilot-EEG.</t>
         </is>
       </c>
     </row>

--- a/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
+++ b/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
@@ -670,8 +670,8 @@
       <c r="D9" s="8" t="n"/>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Fabian Amlacher (Abteilung: Elektrotechnik) – Kassier; Web-Frontend &amp; -Backend, Serverinfrastruktur (Docker, Datenbank, Backup), EDA-Datenimport, Abrechnungslogik (Rechnungserstellung, SEPA-Lastschrift)
-Alexander Brunner (Abteilung: Elektrotechnik) – Gründungsmitglied; Hardware &amp; Firmware der selbst gebauten P1-Ausleseeinheit (Platine, 3D-Druck, P1-Schnittstelle, MQTT, WLAN)</t>
+          <t>Fabian Amlacher (Abteilung: Elektrotechnik) – Kassier; Plattform (Verwaltung &amp; Anzeige), Serverbetrieb, Einlesen der Verrechnungsdaten, automatisierte Abrechnung &amp; Bankeinzug
+Alexander Brunner (Abteilung: Elektrotechnik) – Gründungsmitglied; Hardware &amp; Firmware der selbst entwickelten Ausleseeinheit für die Zählerdaten</t>
         </is>
       </c>
     </row>
@@ -775,10 +775,10 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Gemeinsam: Aufbau der Plattform „Strom für alle“ – einer mandantenfähigen Webanwendung zur Verwaltung mehrerer Energiegemeinschaften (Mitglieder, Zählpunkte, Verträge, Tarife, Abrechnung) auf Basis von PostgreSQL/TimescaleDB, PHP, nginx/Traefik und Docker. Gemeinsam wird untersucht, wie Echtzeit-Messdaten (ESP32/P1-Schnittstelle) und die offiziellen EDA-Verrechnungsdaten des Netzbetreibers sauber getrennt und für Visualisierung bzw. rechtssichere Abrechnung genutzt werden können, sowie wie eine EAG-/ElWOG-konforme, dynamische Verteilung nach Viertelstundenwerten technisch und organisatorisch umgesetzt wird.
-Patrick Ropper (Obmann): Projektkoordination und Entscheidungsfindung im Team; Gründung und laufende Führung der Pilot-EEG (Statuten, Vertrag mit dem Netzbetreiber KNG-Kärnten Netz inkl. Festlegung des Aufteilungsschlüssels, Tarifgestaltung, steuerliche Beratung); Gesamtarchitektur der Plattform sowie Schnittstelle zwischen technischer Umsetzung und rechtlichen Vorgaben (VerG, ElWOG, EAG, UStG); Sicherheit &amp; Datenschutz (DSGVO, Verschlüsselung, Zugriffsschutz, Demo-Modus) in enger Abstimmung mit Fabian (Webseite) und Alexander (Ausleseeinheit); rechtlich vorgeschriebener Rechnungsinhalt und Rechnungsdesign.
-Fabian Amlacher (Kassier): Aufbau der Serverinfrastruktur (Docker, Traefik, MQTT/Mosquitto, PostgreSQL/TimescaleDB, Backup); Entwicklung von Frontend und Backend der Plattform (Mitgliederverwaltung, Live-Anzeige); Import der manuellen EDA-XLSX-Exporte des Netzbetreibers und Zuordnung der Verbrauchs-/Einspeisewerte je Zählpunkt in der Datenbank; Abrechnungslogik inkl. Rechnungserstellung über einen LaTeX-zu-PDF-Service und Erstellung der SEPA-Lastschrift-Datei für den Bankeinzug.
-Alexander Brunner: Entwicklung von Hardware (Platinen-Design, Bauteilauswahl, 3D-Druck-Gehäuse) und Firmware (P1-Schnittstelle intelligenter Stromzähler, MQTT-Übertragung, WLAN-Setup) der selbst gebauten P1-Ausleseeinheit sowie deren Inbetriebnahme und Test.</t>
+          <t>Gemeinsam: Aufbau der Plattform „Strom für alle“ – einer mandantenfähigen Webanwendung zur Verwaltung mehrerer Energiegemeinschaften (Mitglieder, Zählpunkte, Verträge, Tarife, Abrechnung). Gemeinsam wird untersucht, wie Echtzeit-Messdaten der Zählpunkte und die offiziellen Verrechnungsdaten des Netzbetreibers sauber getrennt und für Visualisierung bzw. rechtssichere Abrechnung genutzt werden können, sowie wie eine EAG-/ElWOG-konforme, dynamische Verteilung nach Viertelstundenwerten organisatorisch und technisch umgesetzt werden kann – welche Architektur, Werkzeuge und Verfahren sich dafür jeweils am besten eignen, ist selbst Teil der Untersuchung.
+Patrick Ropper (Obmann): Projektkoordination und Entscheidungsfindung im Team; Gründung und laufende Führung der Pilot-EEG (Statuten, Vertrag mit dem Netzbetreiber KNG-Kärnten Netz inkl. Festlegung des Aufteilungsschlüssels, Tarifgestaltung, steuerliche Beratung); Gesamtarchitektur der Plattform sowie Schnittstelle zwischen technischer Umsetzung und rechtlichen Vorgaben (VerG, ElWOG, EAG, UStG); wie Sicherheit und Datenschutz (u.a. DSGVO-Vorgaben, Zugriffsschutz) in einer solchen Plattform sinnvoll umgesetzt werden können, in enger Abstimmung mit Fabian und Alexander; rechtlich vorgeschriebener Rechnungsinhalt und Rechnungsdesign.
+Fabian Amlacher (Kassier): Wie eine zuverlässige, wartbare Serverinfrastruktur für eine solche Plattform aufgebaut werden kann; Entwicklung von Frontend und Backend (Mitgliederverwaltung, Live-Anzeige); wie die vom Netzbetreiber bereitgestellten Verrechnungsdaten automatisiert eingelesen und den richtigen Zählpunkten zugeordnet werden können; wie daraus automatisiert korrekte Rechnungen sowie ein Sammellastschrift-Auftrag für den Bankeinzug erzeugt werden können.
+Alexander Brunner: Entwicklung einer eigenen Hardware (Platine, Bauteilauswahl, Gehäuse) zum Auslesen der P1-Schnittstelle intelligenter Stromzähler sowie der dazugehörigen Firmware zur zuverlässigen, sicheren Übertragung der Messdaten; Inbetriebnahme und Test bei realen Mitgliedern.</t>
         </is>
       </c>
     </row>
@@ -832,9 +832,9 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Patrick Ropper: Eine im Verein eingetragene und beim Netzbetreiber aktive Energiegemeinschaft (Statuten, Mitgliederverträge, Tarifblatt, AGB), eine dokumentierte Gesamtarchitektur und Projektsteuerung sowie ein datenschutz- und sicherheitskonform umgesetztes Konzept (DSGVO, Verschlüsselung, Zugriffsschutz) der Plattform Strom für alle.
-Fabian Amlacher: Ein lauffähiges Frontend und Backend der Plattform samt Serverinfrastruktur (Docker, Datenbank, Backup) sowie ein funktionierender EDA-Datenimport und eine automatisierte Abrechnungslogik inkl. Rechnungserstellung (LaTeX zu PDF) und SEPA-Lastschrift-Export.
-Alexander Brunner: Eine selbst entwickelte und gefertigte P1-Ausleseeinheit (Platine, 3D-gedrucktes Gehäuse) mit funktionierender Firmware (P1-Schnittstelle, MQTT-Übertragung, WLAN-Konfiguration), einsatzbereit bei den Mitgliedern der Pilot-EEG.</t>
+          <t>Patrick Ropper: Eine im Verein eingetragene und beim Netzbetreiber aktive Energiegemeinschaft (Statuten, Mitgliederverträge, Tarifblatt, AGB), eine dokumentierte Gesamtarchitektur und Projektsteuerung sowie ein datenschutz- und sicherheitskonform umgesetztes Konzept der Plattform Strom für alle.
+Fabian Amlacher: Eine lauffähige Plattform (Frontend, Backend, Serverbetrieb), die die Verrechnungsdaten des Netzbetreibers automatisiert einliest und daraus korrekte Rechnungen sowie einen Sammellastschrift-Auftrag für den Bankeinzug erzeugt.
+Alexander Brunner: Eine selbst entwickelte und gefertigte Ausleseeinheit (Platine, Gehäuse) mit funktionierender Firmware, die die Messdaten intelligenter Stromzähler zuverlässig überträgt, einsatzbereit bei den Mitgliedern der Pilot-EEG.</t>
         </is>
       </c>
     </row>

--- a/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
+++ b/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>In Kärnten entstehen im Zuge der Energiewende laufend neue Energiegemeinschaften (EEGs), doch es fehlt an einer leistbaren, mandantenfähigen Software zur Verwaltung von Mitgliedern, Zählpunkten, Tarifen und Abrechnung. Bestehende Lösungen sind für kleine regionale EEGs zu teuer oder zu komplex. Als Praxisbasis wurde die Pilot-EEG „Strompool Feldkirchen Süd-West“ bereits gegründet.</t>
+          <t>In Kärnten entstehen im Zuge der Energiewende laufend neue Energiegemeinschaften (EEGs), doch es fehlt an einer leistbaren, mandantenfähigen Software zur Verwaltung von Mitgliedern, Zählpunkten, Tarifen und Abrechnung. Bestehende Lösungen sind für kleine regionale EEGs zu teuer oder zu komplex. Als Praxisbasis soll die Pilot-EEG „Strompool Feldkirchen Süd-West“ gegründet und aufgebaut werden.</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Gemeinsam: Aufbau der Plattform „Strom für alle“ – einer mandantenfähigen Webanwendung zur Verwaltung mehrerer Energiegemeinschaften (Mitglieder, Zählpunkte, Verträge, Tarife, Abrechnung). Gemeinsam wird untersucht, wie Echtzeit-Messdaten der Zählpunkte und die offiziellen Verrechnungsdaten des Netzbetreibers sauber getrennt und für Visualisierung bzw. rechtssichere Abrechnung genutzt werden können, sowie wie eine EAG-/ElWOG-konforme, dynamische Verteilung nach Viertelstundenwerten organisatorisch und technisch umgesetzt werden kann – welche Architektur, Werkzeuge und Verfahren sich dafür jeweils am besten eignen, ist selbst Teil der Untersuchung.
-Patrick Ropper (Obmann): Projektkoordination und Entscheidungsfindung im Team; Gründung und laufende Führung der Pilot-EEG (Statuten, Vertrag mit dem Netzbetreiber KNG-Kärnten Netz inkl. Festlegung des Aufteilungsschlüssels, Tarifgestaltung, steuerliche Beratung); Gesamtarchitektur der Plattform sowie Schnittstelle zwischen technischer Umsetzung und rechtlichen Vorgaben (VerG, ElWOG, EAG, UStG); wie Sicherheit und Datenschutz (u.a. DSGVO-Vorgaben, Zugriffsschutz) in einer solchen Plattform sinnvoll umgesetzt werden können, in enger Abstimmung mit Fabian und Alexander; rechtlich vorgeschriebener Rechnungsinhalt und Rechnungsdesign.
+Patrick Ropper (Obmann): Projektkoordination und Entscheidungsfindung im Team; Gründung und laufende Führung der Pilot-EEG (Statuten, Vertrag mit dem Netzbetreiber KNG-Kärnten Netz inkl. Festlegung des Aufteilungsschlüssels, Tarifgestaltung, steuerliche Beratung); Gesamtarchitektur der Plattform sowie Schnittstelle zwischen technischer Umsetzung und rechtlichen Vorgaben (VerG, ElWOG, EAG, UStG); wie Sicherheit und Datenschutz in einer solchen Plattform sinnvoll umgesetzt werden können, in enger Abstimmung mit Fabian und Alexander; rechtlich vorgeschriebener Rechnungsinhalt und Rechnungsdesign.
 Fabian Amlacher (Kassier): Wie eine zuverlässige, wartbare Serverinfrastruktur für eine solche Plattform aufgebaut werden kann; Entwicklung von Frontend und Backend (Mitgliederverwaltung, Live-Anzeige); wie die vom Netzbetreiber bereitgestellten Verrechnungsdaten automatisiert eingelesen und den richtigen Zählpunkten zugeordnet werden können; wie daraus automatisiert korrekte Rechnungen sowie ein Sammellastschrift-Auftrag für den Bankeinzug erzeugt werden können.
 Alexander Brunner: Entwicklung einer eigenen Hardware (Platine, Bauteilauswahl, Gehäuse) zum Auslesen der P1-Schnittstelle intelligenter Stromzähler sowie der dazugehörigen Firmware zur zuverlässigen, sicheren Übertragung der Messdaten; Inbetriebnahme und Test bei realen Mitgliedern.</t>
         </is>
@@ -857,12 +857,13 @@
       <c r="D16" s="10" t="n"/>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>(Portal akzeptiert nur zukünftige Termine – bereits erledigte Schritte wie Vereinsgründung, KNG-Vertrag etc. sind daher hier nicht mehr gelistet.)
+          <t>❓ Datum: Vereinsgründung &amp; Statuten der Pilot-EEG
+❓ Datum: Vertragsabschluss mit dem Netzbetreiber (KNG)
 ❓ Datum: Zwischenpräsentation der Diplomarbeit
-❓ Datum: Fertigstellung Paket 2 – Abrechnung (pdflatex-Bug &amp; EDA-Upload-Fehler beheben, Ende-zu-Ende-Billing)
+❓ Datum: Fertigstellung Paket 2 – Abrechnung
 ❓ Datum: Fertigstellung Paket 3 – Backup-Monitor für Admins
 ❓ Datum: SEPA-Lastschrift – Creditor-ID-Antrag abschließen
-❓ Datum: Klärung KNG-Datenfreigabe-Prozess (Sammel-Vollmacht vs. Einzel-Login je Mitglied)
+❓ Datum: Klärung KNG-Datenfreigabe-Prozess
 ❓ Datum: Dokumentation &amp; Abschluss
 ❓ Datum: Abgabe der Diplomarbeit (siehe Zeile 6)</t>
         </is>

--- a/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
+++ b/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
@@ -90,7 +90,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -121,6 +121,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -425,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83203125" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="21.33" customWidth="1" style="4" min="1" max="1"/>
@@ -463,22 +466,22 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="5">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Typ der Arbeit</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>Art der Arbeit auswählen (z. B. Diplomarbeit).</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>Art der Arbeit auswählen.</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>Diplomarbeit</t>
         </is>
@@ -489,77 +492,77 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="5">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="3" ht="26.85" customHeight="1" s="5">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Schulart</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Die zutreffende Schulart eintragen (z. B. HTL).</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>HTL</t>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Schulart-Kategorie im Dropdown auswählen (HTL fällt darunter).</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Dropdown-Wert lt. Portal</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>HTL</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26.85" customHeight="1" s="5">
-      <c r="A4" s="8" t="inlineStr">
+          <t>Technische, gewerbliche und kunstgewerbliche Schulen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="55" customHeight="1" s="5">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Thema</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Den gemeinsamen Haupttitel des Projekts formulieren (z. B. Entwicklung und Aufbau eines elektrischen Antriebstrangs...).</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Den gemeinsamen Haupttitel des Projekts formulieren.</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>(Erforderlich), max. 200 Zeichen</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Strom für alle - Entwicklung einer digitalen Plattform samt eigener P1-Ausleseeinheit für Echtzeit-Verbrauchsanzeige und automatisierte Abrechnung am Pilotprojekt Strompool Feldkirchen Süd-West</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="26.85" customHeight="1" s="5">
-      <c r="A5" s="8" t="inlineStr">
+          <t>Strom für alle - Entwicklung einer digitalen Plattform samt eigener Ausleseeinheit für Echtzeit-Verbrauchsanzeige und automatisierte Abrechnung am Pilotprojekt Strompool Feldkirchen Süd-West</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="5">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Verantwortliche/r Schüler/in</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Den/Die Projektleiter/in aus dem Team nominieren und eintragen.</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Den/Die Projektleiter/in aus dem Team nominieren.</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>(Erforderlich)</t>
         </is>
@@ -570,267 +573,585 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="26.85" customHeight="1" s="5">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="5">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Verordneter, spätester Abgabetermin</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Das von der Schule vorgegebene finale Abgabedatum eintragen.</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>(Erforderlich)</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>❓ offen – macht Patrick selbst noch fertig</t>
+          <t>❓ offen – trägst du direkt im Portal ein</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26.85" customHeight="1" s="5">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Sperrvermerk</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Checkbox: Soll die Arbeit unter Verschluss gehalten werden?</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Ja/Nein</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Nein (Vorschlag – bitte von Patrick bestätigen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="5">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Klasse (Verantwortliche/r)</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Aktuelle Schulklasse des Hauptverantwortlichen.</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>(Erforderlich)</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>❓ offen – trägst du direkt im Portal ein</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="5">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Abteilung (Verantwortliche/r)</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Fachrichtung/Abteilung des Hauptverantwortlichen.</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>(Erforderlich)</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>❓ offen – trägst du direkt im Portal ein</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="55" customHeight="1" s="5">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Individuelle Themenstellung (Verantwortliche/r)</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Den Kurztitel des persönlichen Aufgabenbereichs des/der Hauptverantwortlichen eintragen.</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Den Kurztitel des persönlichen Aufgabenbereichs eintragen.</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>(Erforderlich), max. 200 Zeichen</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Vereinsführung, Netzbetreiber-Vertrag &amp; Tarife (Obmann); Gesamtarchitektur &amp; Projektleitung; Sicherheit &amp; Datenschutz der Plattform Strom für alle</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26.85" customHeight="1" s="5">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Vereinsgründung, Netzbetreiber-Anbindung &amp; Tarifgestaltung (offene Recherche); Gesamtarchitektur &amp; Projektleitung; Sicherheit &amp; Datenschutz der Plattform Strom für alle</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="5">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Allgemein</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Geschätzter Arbeitsaufwand</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Die geschätzten Projektstunden für den verantwortlichen Schüler angeben.</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Geschätzter Arbeitsaufwand (Verantwortliche/r)</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Die geschätzten Projektstunden angeben.</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>(Erforderlich)</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>180 Stunden</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1" s="5">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="5">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Beteiligte SchülerInnen</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Schüler/in &amp; individuelle Themenstellung</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Alle weiteren Teammitglieder, deren Abteilung (z. B. ET) und den Kurztitel ihres jeweiligen Teilbereichs eintragen. Markieren, wer hauptverantwortlich ist.</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>Fabian Amlacher (Abteilung: Elektrotechnik) – Kassier; Plattform (Verwaltung &amp; Anzeige), Serverbetrieb, Einlesen der Verrechnungsdaten, automatisierte Abrechnung &amp; Bankeinzug
-Alexander Brunner (Abteilung: Elektrotechnik) – Gründungsmitglied; Hardware &amp; Firmware der selbst entwickelten Ausleseeinheit für die Zählerdaten</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="45" customHeight="1" s="5">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Schüler/in 2 – Name</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Weiteres Teammitglied aus der Liste wählen.</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Fabian Amlacher</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="5">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Beteiligte SchülerInnen</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Schüler/in 2 – Klasse</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Aktuelle Schulklasse eintragen.</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>❓ offen – trägst du direkt im Portal ein</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="5">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Beteiligte SchülerInnen</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Schüler/in 2 – Abteilung</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Fachrichtung/Abteilung eintragen.</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>❓ offen – trägst du direkt im Portal ein</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1" s="5">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Beteiligte SchülerInnen</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Schüler/in 2 – Individuelle Themenstellung</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Kurztitel des persönlichen Teilbereichs eintragen.</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>max. 200 Zeichen</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Plattform (Verwaltung &amp; Anzeige), Serverbetrieb, Einlesen der Verrechnungsdaten, automatisierte Abrechnung &amp; Bankeinzug</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="5">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Beteiligte SchülerInnen</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Schüler/in 2 – Geschätzter Arbeitsaufwand</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Geschätzte Projektstunden angeben.</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>❓ offen – trägst du direkt im Portal ein</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="5">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Beteiligte SchülerInnen</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Schüler/in 3 – Name</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Weiteres Teammitglied aus der Liste wählen.</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Alexander Brunner</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="5">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Beteiligte SchülerInnen</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Schüler/in 3 – Klasse</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Aktuelle Schulklasse eintragen.</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>❓ offen – trägst du direkt im Portal ein</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="5">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Beteiligte SchülerInnen</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Schüler/in 3 – Abteilung</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Fachrichtung/Abteilung eintragen.</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>❓ offen – trägst du direkt im Portal ein</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1" s="5">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Beteiligte SchülerInnen</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Schüler/in 3 – Individuelle Themenstellung</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Kurztitel des persönlichen Teilbereichs eintragen.</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>max. 200 Zeichen</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Hardware &amp; Firmware einer eigenen Ausleseeinheit für Zählerdaten (Auslesemethode, z. B. P1-Schnittstelle oder Infrarot, wird evaluiert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="5">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Beteiligte SchülerInnen</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Schüler/in 3 – Geschätzter Arbeitsaufwand</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Geschätzte Projektstunden angeben.</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>❓ offen – trägst du direkt im Portal ein</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="5">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>BetreuerInnen</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Name &amp; Rolle</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Die Lehrkräfte eintragen und deren Rollen (Hauptverantwortliche/r Betreuer/in vs. Betreuer/in) zuweisen.</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>Prof. DI Theodor Kranz – Betreuer (kein weiterer Betreuer)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26.85" customHeight="1" s="5">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Betreuer/in 1 – Name</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Betreuende Lehrkraft eintragen.</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Prof. DI Theodor Kranz</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="5">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>BetreuerInnen</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Betreuer/in 1 – Rolle</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Rolle zuweisen.</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Hauptverantwortliche/r Betreuer/Betreuerin</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="5">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Zusätzliche Information</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Schuljahr der abschließenden Prüfung</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Das Jahr der Matura/Abschlussprüfung eintragen (z. B. 2025/26).</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Das Jahr der Matura/Abschlussprüfung eintragen.</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>(Erforderlich)</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>2026/27</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="85" customHeight="1" s="5">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="25" ht="85" customHeight="1" s="5">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Zusätzliche Information</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Ausgangslage</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Kurze Beschreibung des Ist-Zustands: Warum wird das Projekt gemacht? Was fehlt bisher? (Z. B. "Bisher kein E-Go-Kart an der HTL1...").</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Kurze Beschreibung des Ist-Zustands: Warum wird das Projekt gemacht? Was fehlt bisher?</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>(Erforderlich), max. 400 Zeichen</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>In Kärnten entstehen im Zuge der Energiewende laufend neue Energiegemeinschaften (EEGs), doch es fehlt an einer leistbaren, mandantenfähigen Software zur Verwaltung von Mitgliedern, Zählpunkten, Tarifen und Abrechnung. Bestehende Lösungen sind für kleine regionale EEGs zu teuer oder zu komplex. Als Praxisbasis soll die Pilot-EEG „Strompool Feldkirchen Süd-West“ gegründet und aufgebaut werden.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="260" customHeight="1" s="5">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="26" ht="260" customHeight="1" s="5">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Zusätzliche Information</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Untersuchungsanliegen (individuell &amp; gemeinsam)</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Detaillierte technische Beschreibung: Was genau macht jeder Schüler? Welche Aufgaben werden gemeinsam gelöst? (z.B. Motorauswahl, Batteriemanagement).</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Untersuchungsanliegen der individuellen Themenstellungen</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Detaillierte Beschreibung: Was untersucht/macht jede/r Einzelne, was gemeinsam?</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>(Erforderlich), max. 2400 Zeichen</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>Gemeinsam: Aufbau der Plattform „Strom für alle“ – einer mandantenfähigen Webanwendung zur Verwaltung mehrerer Energiegemeinschaften (Mitglieder, Zählpunkte, Verträge, Tarife, Abrechnung). Gemeinsam wird untersucht, wie Echtzeit-Messdaten der Zählpunkte und die offiziellen Verrechnungsdaten des Netzbetreibers sauber getrennt und für Visualisierung bzw. rechtssichere Abrechnung genutzt werden können, sowie wie eine EAG-/ElWOG-konforme, dynamische Verteilung nach Viertelstundenwerten organisatorisch und technisch umgesetzt werden kann – welche Architektur, Werkzeuge und Verfahren sich dafür jeweils am besten eignen, ist selbst Teil der Untersuchung.
-Patrick Ropper (Obmann): Projektkoordination und Entscheidungsfindung im Team; Gründung und laufende Führung der Pilot-EEG (Statuten, Vertrag mit dem Netzbetreiber KNG-Kärnten Netz inkl. Festlegung des Aufteilungsschlüssels, Tarifgestaltung, steuerliche Beratung); Gesamtarchitektur der Plattform sowie Schnittstelle zwischen technischer Umsetzung und rechtlichen Vorgaben (VerG, ElWOG, EAG, UStG); wie Sicherheit und Datenschutz in einer solchen Plattform sinnvoll umgesetzt werden können, in enger Abstimmung mit Fabian und Alexander; rechtlich vorgeschriebener Rechnungsinhalt und Rechnungsdesign.
-Fabian Amlacher (Kassier): Wie eine zuverlässige, wartbare Serverinfrastruktur für eine solche Plattform aufgebaut werden kann; Entwicklung von Frontend und Backend (Mitgliederverwaltung, Live-Anzeige); wie die vom Netzbetreiber bereitgestellten Verrechnungsdaten automatisiert eingelesen und den richtigen Zählpunkten zugeordnet werden können; wie daraus automatisiert korrekte Rechnungen sowie ein Sammellastschrift-Auftrag für den Bankeinzug erzeugt werden können.
-Alexander Brunner: Entwicklung einer eigenen Hardware (Platine, Bauteilauswahl, Gehäuse) zum Auslesen der P1-Schnittstelle intelligenter Stromzähler sowie der dazugehörigen Firmware zur zuverlässigen, sicheren Übertragung der Messdaten; Inbetriebnahme und Test bei realen Mitgliedern.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="85" customHeight="1" s="5">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Gemeinsam: Aufbau der Plattform „Strom für alle“ – einer mandantenfähigen Webanwendung zur Verwaltung mehrerer Energiegemeinschaften (Mitglieder, Zählpunkte, Verträge, Tarife, Abrechnung). Gemeinsam wird untersucht, wie Zählerdaten technisch zuverlässig ausgelesen werden können (z. B. über die P1-Schnittstelle oder optisch/Infrarot), wie diese Echtzeit-Messdaten und die offiziellen Verrechnungsdaten des Netzbetreibers sauber getrennt und für Visualisierung bzw. rechtssichere Abrechnung genutzt werden können, sowie wie eine EAG-/ElWOG-konforme, dynamische Verteilung nach Viertelstundenwerten organisatorisch und technisch umgesetzt werden kann – welche Architektur, Werkzeuge und Verfahren sich dafür jeweils am besten eignen, ist selbst Teil der Untersuchung.
+Patrick Ropper: Wie ein Verein gegründet und geführt werden muss (Statuten, Organe, Ablauf); welche Vereinbarungen mit dem Netzbetreiber (voraussichtlich Kärnten Netz) für eine Energiegemeinschaft nötig sind, inkl. Tarifgestaltung und Aufteilungsschlüssel; Gesamtarchitektur der Plattform sowie Schnittstelle zwischen technischer Umsetzung und rechtlichen Vorgaben (VerG, ElWOG, EAG, UStG); wie Sicherheit und Datenschutz in einer solchen Plattform sinnvoll umgesetzt werden können, in enger Abstimmung mit Fabian und Alexander; rechtlich vorgeschriebener Rechnungsinhalt und Rechnungsdesign.
+Fabian Amlacher: Wie eine zuverlässige, wartbare Serverinfrastruktur für eine solche Plattform aufgebaut werden kann; Entwicklung von Frontend und Backend (Mitgliederverwaltung, Live-Anzeige); wie die vom Netzbetreiber bereitgestellten Verrechnungsdaten automatisiert eingelesen und den richtigen Zählpunkten zugeordnet werden können; wie daraus automatisiert korrekte Rechnungen sowie ein Sammellastschrift-Auftrag für den Bankeinzug erzeugt werden können.
+Alexander Brunner: Entwicklung einer eigenen Hardware (Platine, Bauteilauswahl, Gehäuse) zur Auslesung der Zählerdaten – welche Schnittstelle (z. B. P1 oder optisch/Infrarot) sich dafür am besten eignet, ist Teil der Untersuchung – sowie der dazugehörigen Firmware zur zuverlässigen, sicheren Übertragung der Messdaten; Inbetriebnahme und Test bei realen Mitgliedern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="85" customHeight="1" s="5">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Zusätzliche Information</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Zielsetzung</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Kurze Zusammenfassung des Soll-Zustands: Was ist das finale Ziel des Projekts? (z.B. funktionsfähiger Antriebsstrang nach ZEC-Reglement).</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Kurze Zusammenfassung des Soll-Zustands: Was ist das finale Ziel des Projekts?</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>(Erforderlich), max. 400 Zeichen</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>Ziel ist eine funktionsfähige, mandantenfähige Plattform „Strom für alle“, die die Pilot-EEG Strompool Feldkirchen Süd-West vollständig abbildet: von der Mitgliederverwaltung über die automatisierte, rechtskonforme Abrechnung bis zur Echtzeit-Visualisierung der Zählerdaten. Die EEG soll damit im laufenden Betrieb funktionieren und als Vorlage für weitere Energiegemeinschaften dienen.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="220" customHeight="1" s="5">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="28" ht="220" customHeight="1" s="5">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Zusätzliche Information</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Geplantes Ergebnis der individuellen Themenstellungen</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Das konkrete Endprodukt / Ergebnis jedes einzelnen Schülers beschreiben (z. B. funktionsfähiger Prototyp des Antriebs vs. des Batteriesystems).</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Das konkrete Endprodukt/Ergebnis jedes einzelnen Schülers beschreiben.</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>(Erforderlich), max. 2400 Zeichen</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>Patrick Ropper: Eine im Verein eingetragene und beim Netzbetreiber aktive Energiegemeinschaft (Statuten, Mitgliederverträge, Tarifblatt, AGB), eine dokumentierte Gesamtarchitektur und Projektsteuerung sowie ein datenschutz- und sicherheitskonform umgesetztes Konzept der Plattform Strom für alle.
 Fabian Amlacher: Eine lauffähige Plattform (Frontend, Backend, Serverbetrieb), die die Verrechnungsdaten des Netzbetreibers automatisiert einliest und daraus korrekte Rechnungen sowie einen Sammellastschrift-Auftrag für den Bankeinzug erzeugt.
@@ -838,34 +1159,219 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="220" customHeight="1" s="5">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="29" ht="40" customHeight="1" s="5">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Meilensteine</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Meilenstein &amp; Datum</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Wichtige Zwischenschritte des Projekts definieren und mit realistischen Zieldaten (Deadlines) versehen.</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>❓ Datum: Vereinsgründung &amp; Statuten der Pilot-EEG
-❓ Datum: Vertragsabschluss mit dem Netzbetreiber (KNG)
-❓ Datum: Zwischenpräsentation der Diplomarbeit
-❓ Datum: Fertigstellung Paket 2 – Abrechnung
-❓ Datum: Fertigstellung Paket 3 – Backup-Monitor für Admins
-❓ Datum: SEPA-Lastschrift – Creditor-ID-Antrag abschließen
-❓ Datum: Klärung KNG-Datenfreigabe-Prozess
-❓ Datum: Dokumentation &amp; Abschluss
-❓ Datum: Abgabe der Diplomarbeit (siehe Zeile 6)</t>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Meilenstein 1</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>Label: Vereinsgründung &amp; Statuten der Pilot-EEG
+Datum: ❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1" s="5">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Meilensteine</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Meilenstein 2</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>Label: Vertragsabschluss mit dem Netzbetreiber (KNG)
+Datum: ❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1" s="5">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Meilensteine</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Meilenstein 3</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>Label: Zwischenpräsentation der Diplomarbeit
+Datum: ❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1" s="5">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Meilensteine</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Meilenstein 4</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>Label: Fertigstellung Paket 2 – Abrechnung
+Datum: ❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1" s="5">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Meilensteine</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Meilenstein 5</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>Label: Fertigstellung Paket 3 – Backup-Monitor für Admins
+Datum: ❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1" s="5">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Meilensteine</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Meilenstein 6</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>Label: SEPA-Lastschrift – Creditor-ID-Antrag abschließen
+Datum: ❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="40" customHeight="1" s="5">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Meilensteine</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Meilenstein 7</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>Label: Klärung KNG-Datenfreigabe-Prozess
+Datum: ❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="40" customHeight="1" s="5">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Meilensteine</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Meilenstein 8</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>Label: Dokumentation &amp; Abschluss
+Datum: ❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1" s="5">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Meilensteine</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Meilenstein 9</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Label: Abgabe der Diplomarbeit (siehe Zeile 6 „Abgabetermin“)
+Datum: ❓</t>
         </is>
       </c>
     </row>

--- a/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
+++ b/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83203125" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="21.33" customWidth="1" style="4" min="1" max="1"/>
@@ -542,7 +542,7 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Strom für alle - Entwicklung einer digitalen Plattform samt eigener Ausleseeinheit für Echtzeit-Verbrauchsanzeige und automatisierte Abrechnung am Pilotprojekt Strompool Feldkirchen Süd-West</t>
+          <t>Strom für alle - Entwicklung einer digitalen Plattform samt Ausleseeinheit für Echtzeit-Verbrauchsanzeige und automatisierte Abrechnung für die Energiegemeinschaft Strompool Feldkirchen Südwest</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Vereinsgründung, Netzbetreiber-Anbindung &amp; Tarifgestaltung (offene Recherche); Gesamtarchitektur &amp; Projektleitung; Sicherheit &amp; Datenschutz der Plattform Strom für alle</t>
+          <t>Vereinsgründung, Netzbetreiber-Anbindung &amp; Tarifgestaltung (offene Recherche); Gesamtarchitektur &amp; Projektleitung; Datenschutzerklärung der Plattform Strom für alle</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="40" customHeight="1" s="5">
+    <row r="15" ht="55" customHeight="1" s="5">
       <c r="A15" s="11" t="inlineStr">
         <is>
           <t>Beteiligte SchülerInnen</t>
@@ -827,7 +827,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Plattform (Verwaltung &amp; Anzeige), Serverbetrieb, Einlesen der Verrechnungsdaten, automatisierte Abrechnung &amp; Bankeinzug</t>
+          <t>Echtzeit-Anzeige der in der Energiegemeinschaft verfügbaren Energie, sichere Datentrennung &amp; -verarbeitung, Serverbetrieb, Einlesen der Verrechnungsdaten, automatisierte Abrechnung &amp; Bankeinzug</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="85" customHeight="1" s="5">
+    <row r="25" ht="100" customHeight="1" s="5">
       <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Zusätzliche Information</t>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Ausgangslage</t>
+          <t>Ausgangslage – Variante A (erste Wahl: Echtzeit-Problem)</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>In Kärnten entstehen im Zuge der Energiewende laufend neue Energiegemeinschaften (EEGs), doch es fehlt an einer leistbaren, mandantenfähigen Software zur Verwaltung von Mitgliedern, Zählpunkten, Tarifen und Abrechnung. Bestehende Lösungen sind für kleine regionale EEGs zu teuer oder zu komplex. Als Praxisbasis soll die Pilot-EEG „Strompool Feldkirchen Süd-West“ gegründet und aufgebaut werden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="260" customHeight="1" s="5">
+          <t>In Energiegemeinschaften (EEGs) weiß in der Praxis kaum jemand, wie viel Strom gerade gemeinschaftlich verfügbar ist – Netzbetreiber liefern Verbrauchsdaten meist erst am Folgetag. Verbraucht z. B. ein Einspeiser an einem sonnigen Tag selbst viel Strom, den er einspeisen wollte, schalten andere Mitglieder in der Annahme eines Überschusses Geräte zu und beziehen unbemerkt aus dem Netz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="100" customHeight="1" s="5">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Zusätzliche Information</t>
@@ -1081,105 +1081,108 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
+          <t>Ausgangslage – Variante B (Alternative, zur Abstimmung mit Prof. Kranz)</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Zweite Formulierung zur Auswahl – falls Kranz den Software-/Marktlücken-Fokus bevorzugt.</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>max. 400 Zeichen, NUR falls Variante A verworfen wird</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>In Kärnten entstehen im Zuge der Energiewende neue Energiegemeinschaften (EEGs), doch es fehlt an einer leistbaren, mandantenfähigen Software zur Verwaltung von Mitgliedern, Zählpunkten, Tarifen und Abrechnung. Bestehende Lösungen sind für kleine regionale EEGs zu teuer oder zu komplex. Als Praxisbasis soll die Energiegemeinschaft Strompool Feldkirchen Südwest gegründet und aufgebaut werden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="280" customHeight="1" s="5">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Zusätzliche Information</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
           <t>Untersuchungsanliegen der individuellen Themenstellungen</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Detaillierte Beschreibung: Was untersucht/macht jede/r Einzelne, was gemeinsam?</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>(Erforderlich), max. 2400 Zeichen</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>Gemeinsam: Aufbau der Plattform „Strom für alle“ – einer mandantenfähigen Webanwendung zur Verwaltung mehrerer Energiegemeinschaften (Mitglieder, Zählpunkte, Verträge, Tarife, Abrechnung). Gemeinsam wird untersucht, wie Zählerdaten technisch zuverlässig ausgelesen werden können (z. B. über die P1-Schnittstelle oder optisch/Infrarot), wie diese Echtzeit-Messdaten und die offiziellen Verrechnungsdaten des Netzbetreibers sauber getrennt und für Visualisierung bzw. rechtssichere Abrechnung genutzt werden können, sowie wie eine EAG-/ElWOG-konforme, dynamische Verteilung nach Viertelstundenwerten organisatorisch und technisch umgesetzt werden kann – welche Architektur, Werkzeuge und Verfahren sich dafür jeweils am besten eignen, ist selbst Teil der Untersuchung.
-Patrick Ropper: Wie ein Verein gegründet und geführt werden muss (Statuten, Organe, Ablauf); welche Vereinbarungen mit dem Netzbetreiber (voraussichtlich Kärnten Netz) für eine Energiegemeinschaft nötig sind, inkl. Tarifgestaltung und Aufteilungsschlüssel; Gesamtarchitektur der Plattform sowie Schnittstelle zwischen technischer Umsetzung und rechtlichen Vorgaben (VerG, ElWOG, EAG, UStG); wie Sicherheit und Datenschutz in einer solchen Plattform sinnvoll umgesetzt werden können, in enger Abstimmung mit Fabian und Alexander; rechtlich vorgeschriebener Rechnungsinhalt und Rechnungsdesign.
-Fabian Amlacher: Wie eine zuverlässige, wartbare Serverinfrastruktur für eine solche Plattform aufgebaut werden kann; Entwicklung von Frontend und Backend (Mitgliederverwaltung, Live-Anzeige); wie die vom Netzbetreiber bereitgestellten Verrechnungsdaten automatisiert eingelesen und den richtigen Zählpunkten zugeordnet werden können; wie daraus automatisiert korrekte Rechnungen sowie ein Sammellastschrift-Auftrag für den Bankeinzug erzeugt werden können.
-Alexander Brunner: Entwicklung einer eigenen Hardware (Platine, Bauteilauswahl, Gehäuse) zur Auslesung der Zählerdaten – welche Schnittstelle (z. B. P1 oder optisch/Infrarot) sich dafür am besten eignet, ist Teil der Untersuchung – sowie der dazugehörigen Firmware zur zuverlässigen, sicheren Übertragung der Messdaten; Inbetriebnahme und Test bei realen Mitgliedern.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="85" customHeight="1" s="5">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>Gemeinsam: Aufbau der Plattform „Strom für alle“ – einer mandantenfähigen Webanwendung zur Verwaltung mehrerer Energiegemeinschaften (Mitglieder, Zählpunkte, Verträge, Tarife, Abrechnung), mit Pilotbetrieb bei der EEG Strompool Feldkirchen Südwest. Gemeinsam wird untersucht, wie Zählerdaten technisch zuverlässig ausgelesen werden können (z. B. über die P1-Schnittstelle oder optisch/Infrarot), wie diese Echtzeit-Messdaten und die Verrechnungsdaten des Netzbetreibers für Visualisierung bzw. Abrechnung genutzt werden können, sowie wie eine EAG-/ElWOG-konforme, dynamische Verteilung nach Viertelstundenwerten organisatorisch und technisch umgesetzt werden kann – welche Architektur, Werkzeuge und Verfahren sich dafür am besten eignen, ist selbst Teil der Untersuchung.
+Patrick Ropper: Wie ein Verein gegründet und geführt wird (Statuten, Organe, Ablauf); welche Vereinbarungen mit dem Netzbetreiber (voraussichtlich Kärnten Netz) für eine Energiegemeinschaft nötig sind, inkl. Tarifgestaltung und Aufteilungsschlüssel; Gesamtarchitektur der Plattform sowie Schnittstelle zwischen technischer Umsetzung und rechtlichen Vorgaben (VerG, ElWOG, EAG, UStG); welche rechtlichen Datenschutz-Anforderungen (DSGVO) gelten und wie sie in einer Datenschutzerklärung dokumentiert werden (technische Umsetzung der Datentrennung: Fabian); rechtlich vorgeschriebener Rechnungsinhalt und Rechnungsdesign.
+Fabian Amlacher: Wie die in der Energiegemeinschaft tatsächlich verfügbare Leistung in Echtzeit sichtbar gemacht werden kann, statt erst am Folgetag wie bei den Netzbetreiber-Daten; wie eine zuverlässige Serverinfrastruktur dafür aufgebaut werden kann; Entwicklung von Frontend und Backend (Mitgliederverwaltung, Live-Anzeige); technische Umsetzung der Datentrennung und sicheren Datenverarbeitung; wie die Verrechnungsdaten des Netzbetreibers automatisiert eingelesen und den richtigen Zählpunkten zugeordnet werden können; wie daraus automatisiert korrekte Rechnungen samt Sammellastschrift-Auftrag für den Bankeinzug erzeugt werden können.
+Alexander Brunner: Entwicklung einer eigenen Hardware (Platine, Bauteilauswahl, Gehäuse) zur Auslesung der Zählerdaten – welche Schnittstelle (P1 oder optisch/Infrarot) sich dafür am besten eignet, ist Teil der Untersuchung – sowie der dazugehörigen Firmware zur zuverlässigen, sicheren Übertragung der Messdaten; Inbetriebnahme und Test bei realen Mitgliedern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="85" customHeight="1" s="5">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Zusätzliche Information</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Zielsetzung</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Kurze Zusammenfassung des Soll-Zustands: Was ist das finale Ziel des Projekts?</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>(Erforderlich), max. 400 Zeichen</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>Ziel ist eine funktionsfähige, mandantenfähige Plattform „Strom für alle“, die die Pilot-EEG Strompool Feldkirchen Süd-West vollständig abbildet: von der Mitgliederverwaltung über die automatisierte, rechtskonforme Abrechnung bis zur Echtzeit-Visualisierung der Zählerdaten. Die EEG soll damit im laufenden Betrieb funktionieren und als Vorlage für weitere Energiegemeinschaften dienen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="220" customHeight="1" s="5">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>Ziel ist eine funktionsfähige, mandantenfähige Plattform „Strom für alle“, die die Energiegemeinschaft (EEG) Strompool Feldkirchen Südwest als Pilotprojekt abbildet: von der Mitgliederverwaltung über die automatisierte Abrechnung bis zur Echtzeit-Visualisierung der verfügbaren Energie. Die EEG soll im laufenden Betrieb funktionieren und als Vorlage für weitere Energiegemeinschaften dienen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="220" customHeight="1" s="5">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Zusätzliche Information</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Geplantes Ergebnis der individuellen Themenstellungen</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Das konkrete Endprodukt/Ergebnis jedes einzelnen Schülers beschreiben.</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>(Erforderlich), max. 2400 Zeichen</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>Patrick Ropper: Eine im Verein eingetragene und beim Netzbetreiber aktive Energiegemeinschaft (Statuten, Mitgliederverträge, Tarifblatt, AGB), eine dokumentierte Gesamtarchitektur und Projektsteuerung sowie ein datenschutz- und sicherheitskonform umgesetztes Konzept der Plattform Strom für alle.
-Fabian Amlacher: Eine lauffähige Plattform (Frontend, Backend, Serverbetrieb), die die Verrechnungsdaten des Netzbetreibers automatisiert einliest und daraus korrekte Rechnungen sowie einen Sammellastschrift-Auftrag für den Bankeinzug erzeugt.
-Alexander Brunner: Eine selbst entwickelte und gefertigte Ausleseeinheit (Platine, Gehäuse) mit funktionierender Firmware, die die Messdaten intelligenter Stromzähler zuverlässig überträgt, einsatzbereit bei den Mitgliedern der Pilot-EEG.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="40" customHeight="1" s="5">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Meilensteine</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Meilenstein 1</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="n"/>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Label: Vereinsgründung &amp; Statuten der Pilot-EEG
-Datum: ❓</t>
+          <t>Patrick Ropper: Eine im Verein eingetragene und beim Netzbetreiber aktive Energiegemeinschaft (Statuten, Mitgliederverträge, Tarifblatt, AGB, Datenschutzerklärung) sowie eine dokumentierte Gesamtarchitektur und Projektsteuerung der Plattform Strom für alle.
+Fabian Amlacher: Eine lauffähige Plattform, die Mitgliedern erstmals in Echtzeit zeigt, wie viel Strom in der Energiegemeinschaft aktuell verfügbar ist bzw. bezogen wird – statt wie bisher üblich erst am Folgetag über die Netzbetreiber-Daten –, inkl. sicherer, korrekt getrennter Verarbeitung der personenbezogenen Daten, sowie automatisiertem Einlesen der Verrechnungsdaten und daraus erzeugten korrekten Rechnungen samt Sammellastschrift-Auftrag für den Bankeinzug.
+Alexander Brunner: Eine selbst entwickelte und gefertigte Ausleseeinheit (Platine, Gehäuse) mit funktionierender Firmware, die die Messdaten der Stromzähler zuverlässig überträgt, einsatzbereit bei den Mitgliedern der Pilot-Energiegemeinschaft.</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1194,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Meilenstein 2</t>
+          <t>Meilenstein 1</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -1202,173 +1205,197 @@
       <c r="D30" s="9" t="n"/>
       <c r="E30" s="9" t="inlineStr">
         <is>
+          <t>Label: Vereinsgründung &amp; Statuten der Energiegemeinschaft
+Datum: ❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1" s="5">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Meilensteine</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Meilenstein 2</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
           <t>Label: Vertragsabschluss mit dem Netzbetreiber (KNG)
 Datum: ❓</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="40" customHeight="1" s="5">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="32" ht="40" customHeight="1" s="5">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>Meilensteine</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>Meilenstein 3</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
         </is>
       </c>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>Label: Zwischenpräsentation der Diplomarbeit
 Datum: ❓</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="40" customHeight="1" s="5">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="33" ht="40" customHeight="1" s="5">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Meilensteine</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Meilenstein 4</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
         </is>
       </c>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>Label: Fertigstellung Paket 2 – Abrechnung
 Datum: ❓</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="40" customHeight="1" s="5">
-      <c r="A33" s="9" t="inlineStr">
+    <row r="34" ht="40" customHeight="1" s="5">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Meilensteine</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>Meilenstein 5</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
         </is>
       </c>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>Label: Fertigstellung Paket 3 – Backup-Monitor für Admins
 Datum: ❓</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="40" customHeight="1" s="5">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="35" ht="40" customHeight="1" s="5">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Meilensteine</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Meilenstein 6</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
         </is>
       </c>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>Label: SEPA-Lastschrift – Creditor-ID-Antrag abschließen
 Datum: ❓</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="40" customHeight="1" s="5">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="36" ht="40" customHeight="1" s="5">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Meilensteine</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>Meilenstein 7</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
         </is>
       </c>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>Label: Klärung KNG-Datenfreigabe-Prozess
 Datum: ❓</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="40" customHeight="1" s="5">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="37" ht="40" customHeight="1" s="5">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Meilensteine</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>Meilenstein 8</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
         </is>
       </c>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>Label: Dokumentation &amp; Abschluss
 Datum: ❓</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="40" customHeight="1" s="5">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="38" ht="40" customHeight="1" s="5">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Meilensteine</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>Meilenstein 9</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Label (max. 100 Zeichen) + Zieldatum einzeln im Portal anlegen.</t>
         </is>
       </c>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>Label: Abgabe der Diplomarbeit (siehe Zeile 6 „Abgabetermin“)
 Datum: ❓</t>

--- a/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
+++ b/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Strom für alle - Entwicklung einer digitalen Plattform samt Ausleseeinheit für Echtzeit-Verbrauchsanzeige und automatisierte Abrechnung für die Energiegemeinschaft Strompool Feldkirchen Südwest</t>
+          <t>Strom für alle - Entwicklung einer Plattform samt Ausleseeinheit für Echtzeit-Verbrauchsanzeige und automatisierte Abrechnung für die Erneuerbare-Energie-Gemeinschaft Strompool Feldkirchen Süd-West</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>In Kärnten entstehen im Zuge der Energiewende neue Energiegemeinschaften (EEGs), doch es fehlt an einer leistbaren, mandantenfähigen Software zur Verwaltung von Mitgliedern, Zählpunkten, Tarifen und Abrechnung. Bestehende Lösungen sind für kleine regionale EEGs zu teuer oder zu komplex. Als Praxisbasis soll die Energiegemeinschaft Strompool Feldkirchen Südwest gegründet und aufgebaut werden.</t>
+          <t>In Kärnten entstehen neue Energiegemeinschaften (EEGs), doch es fehlt an einer leistbaren, mandantenfähigen Software zur Verwaltung von Mitgliedern, Zählpunkten, Tarifen und Abrechnung. Bestehende Lösungen sind für kleine regionale EEGs zu teuer oder zu komplex. Als Praxisbasis soll die Erneuerbare-Energie-Gemeinschaft Strompool Feldkirchen Süd-West gegründet und aufgebaut werden.</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Gemeinsam: Aufbau der Plattform „Strom für alle“ – einer mandantenfähigen Webanwendung zur Verwaltung mehrerer Energiegemeinschaften (Mitglieder, Zählpunkte, Verträge, Tarife, Abrechnung), mit Pilotbetrieb bei der EEG Strompool Feldkirchen Südwest. Gemeinsam wird untersucht, wie Zählerdaten technisch zuverlässig ausgelesen werden können (z. B. über die P1-Schnittstelle oder optisch/Infrarot), wie diese Echtzeit-Messdaten und die Verrechnungsdaten des Netzbetreibers für Visualisierung bzw. Abrechnung genutzt werden können, sowie wie eine EAG-/ElWOG-konforme, dynamische Verteilung nach Viertelstundenwerten organisatorisch und technisch umgesetzt werden kann – welche Architektur, Werkzeuge und Verfahren sich dafür am besten eignen, ist selbst Teil der Untersuchung.
+          <t>Gemeinsam: Aufbau der Plattform „Strom für alle“ – einer mandantenfähigen Webanwendung zur Verwaltung mehrerer Energiegemeinschaften (Mitglieder, Zählpunkte, Verträge, Tarife, Abrechnung), mit Pilotbetrieb bei der EEG Strompool Feldkirchen Süd-West. Gemeinsam wird untersucht, wie Zählerdaten technisch zuverlässig ausgelesen werden können (z. B. über die P1-Schnittstelle oder optisch/Infrarot), wie diese Echtzeit-Messdaten und die Verrechnungsdaten des Netzbetreibers für Visualisierung bzw. Abrechnung genutzt werden können, sowie eine EAG-/ElWOG-konforme, dynamische Verteilung nach Viertelstundenwerten organisatorisch und technisch umgesetzt werden kann – welche Architektur, Werkzeuge und Verfahren sich dafür am besten eignen, ist selbst Teil der Untersuchung.
 Patrick Ropper: Wie ein Verein gegründet und geführt wird (Statuten, Organe, Ablauf); welche Vereinbarungen mit dem Netzbetreiber (voraussichtlich Kärnten Netz) für eine Energiegemeinschaft nötig sind, inkl. Tarifgestaltung und Aufteilungsschlüssel; Gesamtarchitektur der Plattform sowie Schnittstelle zwischen technischer Umsetzung und rechtlichen Vorgaben (VerG, ElWOG, EAG, UStG); welche rechtlichen Datenschutz-Anforderungen (DSGVO) gelten und wie sie in einer Datenschutzerklärung dokumentiert werden (technische Umsetzung der Datentrennung: Fabian); rechtlich vorgeschriebener Rechnungsinhalt und Rechnungsdesign.
 Fabian Amlacher: Wie die in der Energiegemeinschaft tatsächlich verfügbare Leistung in Echtzeit sichtbar gemacht werden kann, statt erst am Folgetag wie bei den Netzbetreiber-Daten; wie eine zuverlässige Serverinfrastruktur dafür aufgebaut werden kann; Entwicklung von Frontend und Backend (Mitgliederverwaltung, Live-Anzeige); technische Umsetzung der Datentrennung und sicheren Datenverarbeitung; wie die Verrechnungsdaten des Netzbetreibers automatisiert eingelesen und den richtigen Zählpunkten zugeordnet werden können; wie daraus automatisiert korrekte Rechnungen samt Sammellastschrift-Auftrag für den Bankeinzug erzeugt werden können.
 Alexander Brunner: Entwicklung einer eigenen Hardware (Platine, Bauteilauswahl, Gehäuse) zur Auslesung der Zählerdaten – welche Schnittstelle (P1 oder optisch/Infrarot) sich dafür am besten eignet, ist Teil der Untersuchung – sowie der dazugehörigen Firmware zur zuverlässigen, sicheren Übertragung der Messdaten; Inbetriebnahme und Test bei realen Mitgliedern.</t>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Ziel ist eine funktionsfähige, mandantenfähige Plattform „Strom für alle“, die die Energiegemeinschaft (EEG) Strompool Feldkirchen Südwest als Pilotprojekt abbildet: von der Mitgliederverwaltung über die automatisierte Abrechnung bis zur Echtzeit-Visualisierung der verfügbaren Energie. Die EEG soll im laufenden Betrieb funktionieren und als Vorlage für weitere Energiegemeinschaften dienen.</t>
+          <t>Ziel ist eine mandantenfähige Plattform „Strom für alle“, die die Erneuerbare-Energie-Gemeinschaft (EEG) Strompool Feldkirchen Süd-West als Pilotprojekt abbildet: von der Mitgliederverwaltung über die automatisierte Abrechnung bis zur Echtzeit-Visualisierung der verfügbaren Energie. Die EEG soll im Betrieb funktionieren und als Vorlage für weitere Energiegemeinschaften dienen.</t>
         </is>
       </c>
     </row>

--- a/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
+++ b/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Vereinsgründung, Netzbetreiber-Anbindung &amp; Tarifgestaltung (offene Recherche); Gesamtarchitektur &amp; Projektleitung; Datenschutzerklärung der Plattform Strom für alle</t>
+          <t>Vereinsgründung &amp; -verwaltung, Mitglieder-Onboarding &amp; Netzbetreiber-Anbindung; Gesamtarchitektur &amp; Projektleitung; Datenschutzerklärung der Plattform Strom für alle</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Echtzeit-Anzeige der in der Energiegemeinschaft verfügbaren Energie, sichere Datentrennung &amp; -verarbeitung, Serverbetrieb, Einlesen der Verrechnungsdaten, automatisierte Abrechnung &amp; Bankeinzug</t>
+          <t>Echtzeit-Anzeige der in der Energiegemeinschaft verfügbaren Energie, sichere Datentrennung &amp; -verarbeitung, Serverbetrieb, automatisierte Abrechnung &amp; Bankeinzug</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Hardware &amp; Firmware einer eigenen Ausleseeinheit für Zählerdaten (Auslesemethode, z. B. P1-Schnittstelle oder Infrarot, wird evaluiert)</t>
+          <t>Hardware &amp; Firmware einer eigenen Ausleseeinheit für die Zählerdaten der Mitglieder</t>
         </is>
       </c>
     </row>
@@ -1123,8 +1123,8 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Gemeinsam: Aufbau der Plattform „Strom für alle“ – einer mandantenfähigen Webanwendung zur Verwaltung mehrerer Energiegemeinschaften (Mitglieder, Zählpunkte, Verträge, Tarife, Abrechnung), mit Pilotbetrieb bei der EEG Strompool Feldkirchen Süd-West. Gemeinsam wird untersucht, wie Zählerdaten technisch zuverlässig ausgelesen werden können (z. B. über die P1-Schnittstelle oder optisch/Infrarot), wie diese Echtzeit-Messdaten und die Verrechnungsdaten des Netzbetreibers für Visualisierung bzw. Abrechnung genutzt werden können, sowie eine EAG-/ElWOG-konforme, dynamische Verteilung nach Viertelstundenwerten organisatorisch und technisch umgesetzt werden kann – welche Architektur, Werkzeuge und Verfahren sich dafür am besten eignen, ist selbst Teil der Untersuchung.
-Patrick Ropper: Wie ein Verein gegründet und geführt wird (Statuten, Organe, Ablauf); welche Vereinbarungen mit dem Netzbetreiber (voraussichtlich Kärnten Netz) für eine Energiegemeinschaft nötig sind, inkl. Tarifgestaltung und Aufteilungsschlüssel; Gesamtarchitektur der Plattform sowie Schnittstelle zwischen technischer Umsetzung und rechtlichen Vorgaben (VerG, ElWOG, EAG, UStG); welche rechtlichen Datenschutz-Anforderungen (DSGVO) gelten und wie sie in einer Datenschutzerklärung dokumentiert werden (technische Umsetzung der Datentrennung: Fabian); rechtlich vorgeschriebener Rechnungsinhalt und Rechnungsdesign.
+          <t>Gemeinsam: Aufbau der Plattform „Strom für alle“ – einer mandantenfähigen Webanwendung zur Verwaltung mehrerer Energiegemeinschaften (Mitglieder, Zählpunkte, Verträge, Tarife, Abrechnung), mit Pilotbetrieb bei der EEG Strompool Feldkirchen Süd-West. Gemeinsam wird untersucht, wie Zählerdaten technisch zuverlässig ausgelesen werden können (z. B. über die P1-Schnittstelle oder optisch/Infrarot), wie diese Echtzeit-Messdaten und die Verrechnungsdaten des Netzbetreibers für Visualisierung bzw. Abrechnung genutzt werden können, sowie eine EAG-/ElWOG-konforme, dynamische Verteilung nach Viertelstundenwerten organisatorisch und technisch umgesetzt werden kann.
+Patrick Ropper: Wie ein Verein gegründet und verwaltet wird (Statuten, Organe, Ablauf); Mitglieder-Onboarding (Aufklärungsgespräche, Ausfüllen der Beitrittserklärungen) sowie Design von Infoblatt, Beitrittserklärung, SEPA-Mandat und Rechnungsinhalt, analog und digital; welche Vereinbarungen mit dem Netzbetreiber (voraussichtlich Kärnten Netz) nötig sind, inkl. Tarifgestaltung und Aufteilungsschlüssel; Gesamtarchitektur der Plattform sowie Schnittstelle zwischen technischer Umsetzung und rechtlichen Vorgaben (VerG, ElWOG, EAG, UStG); welche rechtlichen Datenschutz-Anforderungen (DSGVO) gelten und wie sie in einer Datenschutzerklärung dokumentiert werden (technische Umsetzung der Datentrennung: Fabian).
 Fabian Amlacher: Wie die in der Energiegemeinschaft tatsächlich verfügbare Leistung in Echtzeit sichtbar gemacht werden kann, statt erst am Folgetag wie bei den Netzbetreiber-Daten; wie eine zuverlässige Serverinfrastruktur dafür aufgebaut werden kann; Entwicklung von Frontend und Backend (Mitgliederverwaltung, Live-Anzeige); technische Umsetzung der Datentrennung und sicheren Datenverarbeitung; wie die Verrechnungsdaten des Netzbetreibers automatisiert eingelesen und den richtigen Zählpunkten zugeordnet werden können; wie daraus automatisiert korrekte Rechnungen samt Sammellastschrift-Auftrag für den Bankeinzug erzeugt werden können.
 Alexander Brunner: Entwicklung einer eigenen Hardware (Platine, Bauteilauswahl, Gehäuse) zur Auslesung der Zählerdaten – welche Schnittstelle (P1 oder optisch/Infrarot) sich dafür am besten eignet, ist Teil der Untersuchung – sowie der dazugehörigen Firmware zur zuverlässigen, sicheren Übertragung der Messdaten; Inbetriebnahme und Test bei realen Mitgliedern.</t>
         </is>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Patrick Ropper: Eine im Verein eingetragene und beim Netzbetreiber aktive Energiegemeinschaft (Statuten, Mitgliederverträge, Tarifblatt, AGB, Datenschutzerklärung) sowie eine dokumentierte Gesamtarchitektur und Projektsteuerung der Plattform Strom für alle.
+          <t>Patrick Ropper: Eine im Verein eingetragene und beim Netzbetreiber aktive Energiegemeinschaft mit onboardeten Mitgliedern (Statuten, Infoblatt, Beitrittserklärungen, SEPA-Mandate, Tarifblatt, AGB, Datenschutzerklärung) sowie eine dokumentierte Gesamtarchitektur und Projektsteuerung der Plattform Strom für alle.
 Fabian Amlacher: Eine lauffähige Plattform, die Mitgliedern erstmals in Echtzeit zeigt, wie viel Strom in der Energiegemeinschaft aktuell verfügbar ist bzw. bezogen wird – statt wie bisher üblich erst am Folgetag über die Netzbetreiber-Daten –, inkl. sicherer, korrekt getrennter Verarbeitung der personenbezogenen Daten, sowie automatisiertem Einlesen der Verrechnungsdaten und daraus erzeugten korrekten Rechnungen samt Sammellastschrift-Auftrag für den Bankeinzug.
 Alexander Brunner: Eine selbst entwickelte und gefertigte Ausleseeinheit (Platine, Gehäuse) mit funktionierender Firmware, die die Messdaten der Stromzähler zuverlässig überträgt, einsatzbereit bei den Mitgliedern der Pilot-Energiegemeinschaft.</t>
         </is>

--- a/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
+++ b/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Strom für alle - Entwicklung einer Plattform samt Ausleseeinheit für Echtzeit-Verbrauchsanzeige und automatisierte Abrechnung für die Erneuerbare-Energie-Gemeinschaft Strompool Feldkirchen Süd-West</t>
+          <t>Strom für alle - Echtzeit-Energiemonitoring mit automatisierter Abrechnung</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Vereinsgründung &amp; -verwaltung, Mitglieder-Onboarding &amp; Netzbetreiber-Anbindung; Gesamtarchitektur &amp; Projektleitung; Datenschutzerklärung der Plattform Strom für alle</t>
+          <t>Vereinsgründung &amp; -verwaltung, Mitglieder-Onboarding, Netzbetreiber-Anbindung, Gesamtarchitektur &amp; Projektleitung, Datenschutzerklärung</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Echtzeit-Anzeige der in der Energiegemeinschaft verfügbaren Energie, sichere Datentrennung &amp; -verarbeitung, Serverbetrieb, automatisierte Abrechnung &amp; Bankeinzug</t>
+          <t>Echtzeit-Anzeige der verfügbaren Energie, sichere Datentrennung, Serverbetrieb, automatisierte Abrechnung &amp; Bankeinzug</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Hardware &amp; Firmware einer eigenen Ausleseeinheit für die Zählerdaten der Mitglieder</t>
+          <t>Hardware &amp; Firmware einer eigenen Ausleseeinheit für die Zählerdaten</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>In Energiegemeinschaften (EEGs) weiß in der Praxis kaum jemand, wie viel Strom gerade gemeinschaftlich verfügbar ist – Netzbetreiber liefern Verbrauchsdaten meist erst am Folgetag. Verbraucht z. B. ein Einspeiser an einem sonnigen Tag selbst viel Strom, den er einspeisen wollte, schalten andere Mitglieder in der Annahme eines Überschusses Geräte zu und beziehen unbemerkt aus dem Netz.</t>
+          <t>In Energiegemeinschaften weiß in der Praxis kaum jemand, wie viel Strom gerade gemeinschaftlich verfügbar ist – Netzbetreiber liefern Daten erst am Folgetag. Verbraucht z. B. ein Mitglied gerade selbst viel Strom, schalten andere in der Annahme eines Überschusses Geräte zu und beziehen unbemerkt aus dem Netz.</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>In Kärnten entstehen neue Energiegemeinschaften (EEGs), doch es fehlt an einer leistbaren, mandantenfähigen Software zur Verwaltung von Mitgliedern, Zählpunkten, Tarifen und Abrechnung. Bestehende Lösungen sind für kleine regionale EEGs zu teuer oder zu komplex. Als Praxisbasis soll die Erneuerbare-Energie-Gemeinschaft Strompool Feldkirchen Süd-West gegründet und aufgebaut werden.</t>
+          <t>In Kärnten entstehen laufend neue Energiegemeinschaften, doch es fehlt an leistbarer, mandantenfähiger Software zur Verwaltung von Mitgliedern, Zählpunkten, Tarifen und Abrechnung. Als Praxisbasis soll die Erneuerbare-Energie-Gemeinschaft Strompool Feldkirchen Süd-West aufgebaut werden.</t>
         </is>
       </c>
     </row>
@@ -1123,10 +1123,10 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Gemeinsam: Aufbau der Plattform „Strom für alle“ – einer mandantenfähigen Webanwendung zur Verwaltung mehrerer Energiegemeinschaften (Mitglieder, Zählpunkte, Verträge, Tarife, Abrechnung), mit Pilotbetrieb bei der EEG Strompool Feldkirchen Süd-West. Gemeinsam wird untersucht, wie Zählerdaten technisch zuverlässig ausgelesen werden können (z. B. über die P1-Schnittstelle oder optisch/Infrarot), wie diese Echtzeit-Messdaten und die Verrechnungsdaten des Netzbetreibers für Visualisierung bzw. Abrechnung genutzt werden können, sowie eine EAG-/ElWOG-konforme, dynamische Verteilung nach Viertelstundenwerten organisatorisch und technisch umgesetzt werden kann.
-Patrick Ropper: Wie ein Verein gegründet und verwaltet wird (Statuten, Organe, Ablauf); Mitglieder-Onboarding (Aufklärungsgespräche, Ausfüllen der Beitrittserklärungen) sowie Design von Infoblatt, Beitrittserklärung, SEPA-Mandat und Rechnungsinhalt, analog und digital; welche Vereinbarungen mit dem Netzbetreiber (voraussichtlich Kärnten Netz) nötig sind, inkl. Tarifgestaltung und Aufteilungsschlüssel; Gesamtarchitektur der Plattform sowie Schnittstelle zwischen technischer Umsetzung und rechtlichen Vorgaben (VerG, ElWOG, EAG, UStG); welche rechtlichen Datenschutz-Anforderungen (DSGVO) gelten und wie sie in einer Datenschutzerklärung dokumentiert werden (technische Umsetzung der Datentrennung: Fabian).
-Fabian Amlacher: Wie die in der Energiegemeinschaft tatsächlich verfügbare Leistung in Echtzeit sichtbar gemacht werden kann, statt erst am Folgetag wie bei den Netzbetreiber-Daten; wie eine zuverlässige Serverinfrastruktur dafür aufgebaut werden kann; Entwicklung von Frontend und Backend (Mitgliederverwaltung, Live-Anzeige); technische Umsetzung der Datentrennung und sicheren Datenverarbeitung; wie die Verrechnungsdaten des Netzbetreibers automatisiert eingelesen und den richtigen Zählpunkten zugeordnet werden können; wie daraus automatisiert korrekte Rechnungen samt Sammellastschrift-Auftrag für den Bankeinzug erzeugt werden können.
-Alexander Brunner: Entwicklung einer eigenen Hardware (Platine, Bauteilauswahl, Gehäuse) zur Auslesung der Zählerdaten – welche Schnittstelle (P1 oder optisch/Infrarot) sich dafür am besten eignet, ist Teil der Untersuchung – sowie der dazugehörigen Firmware zur zuverlässigen, sicheren Übertragung der Messdaten; Inbetriebnahme und Test bei realen Mitgliedern.</t>
+          <t>Gemeinsam: Aufbau der Plattform „Strom für alle“ für mehrere Energiegemeinschaften, mit Pilotbetrieb bei der EEG Strompool Feldkirchen Süd-West. Untersucht wird, wie Zählerdaten zuverlässig ausgelesen (P1-Schnittstelle oder optisch/Infrarot), wie Echtzeit- und Verrechnungsdaten des Netzbetreibers für Visualisierung bzw. Abrechnung genutzt und wie eine EAG-/ElWOG-konforme, dynamische Verteilung nach Viertelstundenwerten umgesetzt werden kann.
+Patrick Ropper: Wie ein Verein gegründet und verwaltet wird; Mitglieder-Onboarding (Gespräche, Beitrittserklärungen) sowie Design von Infoblatt, Beitrittserklärung, SEPA-Mandat und Rechnungsinhalt; nötige Vereinbarungen mit dem Netzbetreiber (Kärnten Netz), inkl. Tarife und Aufteilungsschlüssel; Gesamtarchitektur und Schnittstelle zwischen Technik und Recht (VerG, ElWOG, EAG, UStG); rechtliche Datenschutz-Anforderungen (DSGVO) und Datenschutzerklärung (technische Datentrennung: Fabian).
+Fabian Amlacher: Wie die verfügbare Leistung der Gemeinschaft in Echtzeit sichtbar gemacht werden kann statt erst am Folgetag; Serverinfrastruktur; Frontend &amp; Backend (Mitgliederverwaltung, Live-Anzeige); technische Datentrennung und sichere Verarbeitung; automatisiertes Einlesen der Verrechnungsdaten und Zuordnung zu Zählpunkten; automatisierte Rechnungserstellung samt Sammellastschrift für den Bankeinzug.
+Alexander Brunner: Entwicklung eigener Hardware (Platine, Bauteile, Gehäuse) zur Auslesung der Zählerdaten – welche Schnittstelle (P1 oder optisch/Infrarot) sich eignet, ist Teil der Untersuchung – sowie der Firmware zur sicheren Übertragung; Inbetriebnahme und Test bei realen Mitgliedern.</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Ziel ist eine mandantenfähige Plattform „Strom für alle“, die die Erneuerbare-Energie-Gemeinschaft (EEG) Strompool Feldkirchen Süd-West als Pilotprojekt abbildet: von der Mitgliederverwaltung über die automatisierte Abrechnung bis zur Echtzeit-Visualisierung der verfügbaren Energie. Die EEG soll im Betrieb funktionieren und als Vorlage für weitere Energiegemeinschaften dienen.</t>
+          <t>Ziel ist eine mandantenfähige Plattform „Strom für alle“ für die Erneuerbare-Energie-Gemeinschaft Strompool Feldkirchen Süd-West: Mitgliederverwaltung, automatisierte Abrechnung und Echtzeit-Visualisierung der verfügbaren Energie – als Vorlage für weitere Energiegemeinschaften.</t>
         </is>
       </c>
     </row>
@@ -1180,9 +1180,9 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Patrick Ropper: Eine im Verein eingetragene und beim Netzbetreiber aktive Energiegemeinschaft mit onboardeten Mitgliedern (Statuten, Infoblatt, Beitrittserklärungen, SEPA-Mandate, Tarifblatt, AGB, Datenschutzerklärung) sowie eine dokumentierte Gesamtarchitektur und Projektsteuerung der Plattform Strom für alle.
-Fabian Amlacher: Eine lauffähige Plattform, die Mitgliedern erstmals in Echtzeit zeigt, wie viel Strom in der Energiegemeinschaft aktuell verfügbar ist bzw. bezogen wird – statt wie bisher üblich erst am Folgetag über die Netzbetreiber-Daten –, inkl. sicherer, korrekt getrennter Verarbeitung der personenbezogenen Daten, sowie automatisiertem Einlesen der Verrechnungsdaten und daraus erzeugten korrekten Rechnungen samt Sammellastschrift-Auftrag für den Bankeinzug.
-Alexander Brunner: Eine selbst entwickelte und gefertigte Ausleseeinheit (Platine, Gehäuse) mit funktionierender Firmware, die die Messdaten der Stromzähler zuverlässig überträgt, einsatzbereit bei den Mitgliedern der Pilot-Energiegemeinschaft.</t>
+          <t>Patrick Ropper: Eine im Verein eingetragene, beim Netzbetreiber aktive Energiegemeinschaft mit onboardeten Mitgliedern (Statuten, Infoblatt, Beitrittserklärungen, SEPA-Mandate, Tarifblatt, AGB, Datenschutzerklärung) sowie dokumentierte Gesamtarchitektur und Projektsteuerung.
+Fabian Amlacher: Eine lauffähige Plattform, die Mitgliedern erstmals in Echtzeit zeigt, wie viel Strom verfügbar ist bzw. bezogen wird – statt erst am Folgetag –, inkl. sicherer Datentrennung sowie automatisiertem Einlesen der Verrechnungsdaten und Rechnungserstellung samt Sammellastschrift-Auftrag.
+Alexander Brunner: Eine selbst entwickelte Ausleseeinheit (Platine, Gehäuse) mit funktionierender Firmware, die Messdaten der Stromzähler zuverlässig überträgt, einsatzbereit bei den Mitgliedern.</t>
         </is>
       </c>
     </row>

--- a/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
+++ b/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
@@ -1153,7 +1153,7 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Ziel ist eine mandantenfähige Plattform „Strom für alle“ für die Erneuerbare-Energie-Gemeinschaft Strompool Feldkirchen Süd-West: Mitgliederverwaltung, automatisierte Abrechnung und Echtzeit-Visualisierung der verfügbaren Energie – als Vorlage für weitere Energiegemeinschaften.</t>
+          <t>Ziel ist eine mandantenfähige Plattform namens „Strom für alle“, die Mitglieder verwaltet, Rechnungen automatisch erstellt und in Echtzeit zeigt, wie viel Energie gerade verfügbar ist. Getestet wird sie an der Erneuerbare-Energie-Gemeinschaft Strompool Feldkirchen Süd-West, soll aber von Anfang an auch weitere Energiegemeinschaften verwalten können.</t>
         </is>
       </c>
     </row>

--- a/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
+++ b/docs/diplomarbeit/Diplomarbeit_ABA_Eintragung.xlsx
@@ -1153,7 +1153,7 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Ziel ist eine mandantenfähige Plattform namens „Strom für alle“, die Mitglieder verwaltet, Rechnungen automatisch erstellt und in Echtzeit zeigt, wie viel Energie gerade verfügbar ist. Getestet wird sie an der Erneuerbare-Energie-Gemeinschaft Strompool Feldkirchen Süd-West, soll aber von Anfang an auch weitere Energiegemeinschaften verwalten können.</t>
+          <t>Ziel ist es, eine mandantenfähige Plattform namens „Strom für alle" zu entwickeln. Sie verwaltet Mitglieder, erstellt Rechnungen automatisch und zeigt in Echtzeit, wie viel Energie gerade verfügbar ist. Getestet wird sie an der Erneuerbare-Energie-Gemeinschaft Strompool Feldkirchen Süd-West. Sie soll aber von Anfang an auch weitere Energiegemeinschaften verwalten können.</t>
         </is>
       </c>
     </row>
